--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2315,6 +2315,2145 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130236750</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>631670</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6664219</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130236803</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>631661</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6664002</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flykt och lockläte</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130236816</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>631624</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6664012</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130236782</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101022</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>631812</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6664082</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130236762</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>631777</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6664346</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130236749</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>631805</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6663985</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130236770</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92094</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>631788</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6664350</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130236781</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92291</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>631621</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6664101</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130236783</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101022</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>631850</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6664146</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130236773</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92094</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>631687</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6664111</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130236753</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>53</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>631776</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6664335</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130236759</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>631838</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6664323</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130236767</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91414</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>631787</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6664306</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130236771</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92094</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>631778</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6664355</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130236758</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96179</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>631702</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6663884</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130236768</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91414</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>631680</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6664120</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130236765</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>631682</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6664177</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130236780</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>631621</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6664176</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130236756</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>631787</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6664350</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130236785</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>631651</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6664180</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130236784</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101022</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>631842</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6664237</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130236774</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>631623</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6664101</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -3098,32 +3098,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236783</v>
+        <v>130236753</v>
       </c>
       <c r="B24" t="n">
-        <v>101022</v>
+        <v>97079</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631850</v>
+        <v>631776</v>
       </c>
       <c r="R24" t="n">
-        <v>6664146</v>
+        <v>6664335</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3292,32 +3292,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130236753</v>
+        <v>130236783</v>
       </c>
       <c r="B26" t="n">
-        <v>97079</v>
+        <v>101022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631776</v>
+        <v>631850</v>
       </c>
       <c r="R26" t="n">
-        <v>6664335</v>
+        <v>6664146</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B35" t="n">
-        <v>8440</v>
+        <v>91939</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R35" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236784</v>
+        <v>130236785</v>
       </c>
       <c r="B36" t="n">
-        <v>101022</v>
+        <v>8440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631842</v>
+        <v>631651</v>
       </c>
       <c r="R36" t="n">
-        <v>6664237</v>
+        <v>6664180</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130236774</v>
+        <v>130236784</v>
       </c>
       <c r="B37" t="n">
-        <v>91939</v>
+        <v>101022</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>631623</v>
+        <v>631842</v>
       </c>
       <c r="R37" t="n">
-        <v>6664101</v>
+        <v>6664237</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
         <v>130236750</v>
       </c>
       <c r="B16" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>130236803</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>130236782</v>
       </c>
       <c r="B19" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>130236762</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>130236749</v>
       </c>
       <c r="B21" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>130236770</v>
       </c>
       <c r="B22" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92291</v>
+        <v>92378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3098,32 +3098,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236753</v>
+        <v>130236783</v>
       </c>
       <c r="B24" t="n">
-        <v>97079</v>
+        <v>101109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631776</v>
+        <v>631850</v>
       </c>
       <c r="R24" t="n">
-        <v>6664335</v>
+        <v>6664146</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3195,32 +3195,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130236773</v>
+        <v>130236753</v>
       </c>
       <c r="B25" t="n">
-        <v>92094</v>
+        <v>97166</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631687</v>
+        <v>631776</v>
       </c>
       <c r="R25" t="n">
-        <v>6664111</v>
+        <v>6664335</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,32 +3292,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130236783</v>
+        <v>130236773</v>
       </c>
       <c r="B26" t="n">
-        <v>101022</v>
+        <v>92181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631850</v>
+        <v>631687</v>
       </c>
       <c r="R26" t="n">
-        <v>6664146</v>
+        <v>6664111</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3392,7 +3392,7 @@
         <v>130236759</v>
       </c>
       <c r="B27" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>130236767</v>
       </c>
       <c r="B28" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>130236771</v>
       </c>
       <c r="B29" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130236758</v>
+        <v>130236768</v>
       </c>
       <c r="B30" t="n">
-        <v>96179</v>
+        <v>91501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631702</v>
+        <v>631680</v>
       </c>
       <c r="R30" t="n">
-        <v>6663884</v>
+        <v>6664120</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130236768</v>
+        <v>130236758</v>
       </c>
       <c r="B31" t="n">
-        <v>91414</v>
+        <v>96266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631680</v>
+        <v>631702</v>
       </c>
       <c r="R31" t="n">
-        <v>6664120</v>
+        <v>6663884</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3877,7 +3877,7 @@
         <v>130236765</v>
       </c>
       <c r="B32" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130236756</v>
       </c>
       <c r="B34" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>130236774</v>
       </c>
       <c r="B35" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>130236784</v>
       </c>
       <c r="B37" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2807,32 +2807,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236770</v>
+        <v>130236749</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>97166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631788</v>
+        <v>631805</v>
       </c>
       <c r="R21" t="n">
-        <v>6664350</v>
+        <v>6663985</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2904,32 +2904,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236749</v>
+        <v>130236770</v>
       </c>
       <c r="B22" t="n">
-        <v>97166</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631805</v>
+        <v>631788</v>
       </c>
       <c r="R22" t="n">
-        <v>6663985</v>
+        <v>6664350</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2807,32 +2807,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236749</v>
+        <v>130236770</v>
       </c>
       <c r="B21" t="n">
-        <v>97166</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631805</v>
+        <v>631788</v>
       </c>
       <c r="R21" t="n">
-        <v>6663985</v>
+        <v>6664350</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2904,32 +2904,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236770</v>
+        <v>130236749</v>
       </c>
       <c r="B22" t="n">
-        <v>92181</v>
+        <v>97166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631788</v>
+        <v>631805</v>
       </c>
       <c r="R22" t="n">
-        <v>6664350</v>
+        <v>6663985</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3098,32 +3098,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236773</v>
+        <v>130236783</v>
       </c>
       <c r="B24" t="n">
-        <v>92181</v>
+        <v>101109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631687</v>
+        <v>631850</v>
       </c>
       <c r="R24" t="n">
-        <v>6664111</v>
+        <v>6664146</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3292,32 +3292,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130236783</v>
+        <v>130236773</v>
       </c>
       <c r="B26" t="n">
-        <v>101109</v>
+        <v>92181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631850</v>
+        <v>631687</v>
       </c>
       <c r="R26" t="n">
-        <v>6664146</v>
+        <v>6664111</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
         <v>130236750</v>
       </c>
       <c r="B16" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>130236782</v>
       </c>
       <c r="B19" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,32 +2807,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236770</v>
+        <v>130236749</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>97169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631788</v>
+        <v>631805</v>
       </c>
       <c r="R21" t="n">
-        <v>6664350</v>
+        <v>6663985</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2904,32 +2904,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236749</v>
+        <v>130236770</v>
       </c>
       <c r="B22" t="n">
-        <v>97166</v>
+        <v>92184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631805</v>
+        <v>631788</v>
       </c>
       <c r="R22" t="n">
-        <v>6663985</v>
+        <v>6664350</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3004,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92378</v>
+        <v>92381</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3098,32 +3098,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236783</v>
+        <v>130236753</v>
       </c>
       <c r="B24" t="n">
-        <v>101109</v>
+        <v>97169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631850</v>
+        <v>631776</v>
       </c>
       <c r="R24" t="n">
-        <v>6664146</v>
+        <v>6664335</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3195,32 +3195,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130236753</v>
+        <v>130236773</v>
       </c>
       <c r="B25" t="n">
-        <v>97166</v>
+        <v>92184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631776</v>
+        <v>631687</v>
       </c>
       <c r="R25" t="n">
-        <v>6664335</v>
+        <v>6664111</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,32 +3292,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130236773</v>
+        <v>130236783</v>
       </c>
       <c r="B26" t="n">
-        <v>92181</v>
+        <v>101112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631687</v>
+        <v>631850</v>
       </c>
       <c r="R26" t="n">
-        <v>6664111</v>
+        <v>6664146</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3392,7 +3392,7 @@
         <v>130236767</v>
       </c>
       <c r="B27" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>130236771</v>
       </c>
       <c r="B29" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>130236758</v>
       </c>
       <c r="B30" t="n">
-        <v>96266</v>
+        <v>96269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>130236768</v>
       </c>
       <c r="B31" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130236756</v>
       </c>
       <c r="B34" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236774</v>
+        <v>130236784</v>
       </c>
       <c r="B35" t="n">
-        <v>92026</v>
+        <v>101112</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631623</v>
+        <v>631842</v>
       </c>
       <c r="R35" t="n">
-        <v>6664101</v>
+        <v>6664237</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B36" t="n">
-        <v>8440</v>
+        <v>92029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R36" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130236784</v>
+        <v>130236785</v>
       </c>
       <c r="B37" t="n">
-        <v>101109</v>
+        <v>8440</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>631842</v>
+        <v>631651</v>
       </c>
       <c r="R37" t="n">
-        <v>6664237</v>
+        <v>6664180</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
         <v>130236750</v>
       </c>
       <c r="B16" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>130236803</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>130236782</v>
       </c>
       <c r="B19" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>130236762</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,32 +2807,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236749</v>
+        <v>130236770</v>
       </c>
       <c r="B21" t="n">
-        <v>97169</v>
+        <v>92210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631805</v>
+        <v>631788</v>
       </c>
       <c r="R21" t="n">
-        <v>6663985</v>
+        <v>6664350</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2904,32 +2904,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236770</v>
+        <v>130236749</v>
       </c>
       <c r="B22" t="n">
-        <v>92184</v>
+        <v>97195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631788</v>
+        <v>631805</v>
       </c>
       <c r="R22" t="n">
-        <v>6664350</v>
+        <v>6663985</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3004,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92381</v>
+        <v>92407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3098,32 +3098,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236753</v>
+        <v>130236773</v>
       </c>
       <c r="B24" t="n">
-        <v>97169</v>
+        <v>92210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631776</v>
+        <v>631687</v>
       </c>
       <c r="R24" t="n">
-        <v>6664335</v>
+        <v>6664111</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3195,32 +3195,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130236773</v>
+        <v>130236753</v>
       </c>
       <c r="B25" t="n">
-        <v>92184</v>
+        <v>97195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631687</v>
+        <v>631776</v>
       </c>
       <c r="R25" t="n">
-        <v>6664111</v>
+        <v>6664335</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3295,7 +3295,7 @@
         <v>130236783</v>
       </c>
       <c r="B26" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>130236767</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>91530</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>130236759</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>130236771</v>
       </c>
       <c r="B29" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>130236758</v>
       </c>
       <c r="B30" t="n">
-        <v>96269</v>
+        <v>96295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>130236768</v>
       </c>
       <c r="B31" t="n">
-        <v>91504</v>
+        <v>91530</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>130236765</v>
       </c>
       <c r="B32" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130236756</v>
       </c>
       <c r="B34" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>130236784</v>
       </c>
       <c r="B35" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>130236774</v>
       </c>
       <c r="B36" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -4165,10 +4165,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236784</v>
+        <v>130236785</v>
       </c>
       <c r="B35" t="n">
-        <v>101138</v>
+        <v>8440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,21 +4176,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631842</v>
+        <v>631651</v>
       </c>
       <c r="R35" t="n">
-        <v>6664237</v>
+        <v>6664180</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236774</v>
+        <v>130236784</v>
       </c>
       <c r="B36" t="n">
-        <v>92055</v>
+        <v>101138</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631623</v>
+        <v>631842</v>
       </c>
       <c r="R36" t="n">
-        <v>6664101</v>
+        <v>6664237</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B37" t="n">
-        <v>8440</v>
+        <v>92055</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R37" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
         <v>130236750</v>
       </c>
       <c r="B16" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>130236782</v>
       </c>
       <c r="B19" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>130236770</v>
       </c>
       <c r="B21" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>130236749</v>
       </c>
       <c r="B22" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>130236773</v>
       </c>
       <c r="B24" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,32 +3195,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130236753</v>
+        <v>130236783</v>
       </c>
       <c r="B25" t="n">
-        <v>97195</v>
+        <v>101139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631776</v>
+        <v>631850</v>
       </c>
       <c r="R25" t="n">
-        <v>6664335</v>
+        <v>6664146</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,32 +3292,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130236783</v>
+        <v>130236753</v>
       </c>
       <c r="B26" t="n">
-        <v>101138</v>
+        <v>97196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631850</v>
+        <v>631776</v>
       </c>
       <c r="R26" t="n">
-        <v>6664146</v>
+        <v>6664335</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3389,32 +3389,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130236767</v>
+        <v>130236759</v>
       </c>
       <c r="B27" t="n">
-        <v>91530</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631787</v>
+        <v>631838</v>
       </c>
       <c r="R27" t="n">
-        <v>6664306</v>
+        <v>6664323</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236759</v>
+        <v>130236767</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>91531</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631838</v>
+        <v>631787</v>
       </c>
       <c r="R28" t="n">
-        <v>6664323</v>
+        <v>6664306</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3586,7 +3586,7 @@
         <v>130236771</v>
       </c>
       <c r="B29" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130236758</v>
+        <v>130236768</v>
       </c>
       <c r="B30" t="n">
-        <v>96295</v>
+        <v>91531</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631702</v>
+        <v>631680</v>
       </c>
       <c r="R30" t="n">
-        <v>6663884</v>
+        <v>6664120</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130236768</v>
+        <v>130236758</v>
       </c>
       <c r="B31" t="n">
-        <v>91530</v>
+        <v>96296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631680</v>
+        <v>631702</v>
       </c>
       <c r="R31" t="n">
-        <v>6664120</v>
+        <v>6663884</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4071,7 +4071,7 @@
         <v>130236756</v>
       </c>
       <c r="B34" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B35" t="n">
-        <v>8440</v>
+        <v>92056</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R35" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236784</v>
+        <v>130236785</v>
       </c>
       <c r="B36" t="n">
-        <v>101138</v>
+        <v>8440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631842</v>
+        <v>631651</v>
       </c>
       <c r="R36" t="n">
-        <v>6664237</v>
+        <v>6664180</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130236774</v>
+        <v>130236784</v>
       </c>
       <c r="B37" t="n">
-        <v>92055</v>
+        <v>101139</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>631623</v>
+        <v>631842</v>
       </c>
       <c r="R37" t="n">
-        <v>6664101</v>
+        <v>6664237</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
         <v>130236750</v>
       </c>
       <c r="B16" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>130236782</v>
       </c>
       <c r="B19" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>130236770</v>
       </c>
       <c r="B21" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>130236749</v>
       </c>
       <c r="B22" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>130236773</v>
       </c>
       <c r="B24" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,32 +3195,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130236783</v>
+        <v>130236753</v>
       </c>
       <c r="B25" t="n">
-        <v>101139</v>
+        <v>97197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631850</v>
+        <v>631776</v>
       </c>
       <c r="R25" t="n">
-        <v>6664146</v>
+        <v>6664335</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,32 +3292,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130236753</v>
+        <v>130236783</v>
       </c>
       <c r="B26" t="n">
-        <v>97196</v>
+        <v>101140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631776</v>
+        <v>631850</v>
       </c>
       <c r="R26" t="n">
-        <v>6664335</v>
+        <v>6664146</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3389,32 +3389,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130236759</v>
+        <v>130236767</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>91532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631838</v>
+        <v>631787</v>
       </c>
       <c r="R27" t="n">
-        <v>6664323</v>
+        <v>6664306</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236767</v>
+        <v>130236759</v>
       </c>
       <c r="B28" t="n">
-        <v>91531</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631787</v>
+        <v>631838</v>
       </c>
       <c r="R28" t="n">
-        <v>6664306</v>
+        <v>6664323</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3586,7 +3586,7 @@
         <v>130236771</v>
       </c>
       <c r="B29" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130236768</v>
+        <v>130236758</v>
       </c>
       <c r="B30" t="n">
-        <v>91531</v>
+        <v>96297</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631680</v>
+        <v>631702</v>
       </c>
       <c r="R30" t="n">
-        <v>6664120</v>
+        <v>6663884</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130236758</v>
+        <v>130236768</v>
       </c>
       <c r="B31" t="n">
-        <v>96296</v>
+        <v>91532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2818</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631702</v>
+        <v>631680</v>
       </c>
       <c r="R31" t="n">
-        <v>6663884</v>
+        <v>6664120</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4071,7 +4071,7 @@
         <v>130236756</v>
       </c>
       <c r="B34" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236774</v>
+        <v>130236785</v>
       </c>
       <c r="B35" t="n">
-        <v>92056</v>
+        <v>8440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631623</v>
+        <v>631651</v>
       </c>
       <c r="R35" t="n">
-        <v>6664101</v>
+        <v>6664180</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B36" t="n">
-        <v>8440</v>
+        <v>92057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R36" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4362,7 +4362,7 @@
         <v>130236784</v>
       </c>
       <c r="B37" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
         <v>130236750</v>
       </c>
       <c r="B16" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>130236803</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>130236782</v>
       </c>
       <c r="B19" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>130236762</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,32 +2807,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236770</v>
+        <v>130236749</v>
       </c>
       <c r="B21" t="n">
-        <v>92212</v>
+        <v>97199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631788</v>
+        <v>631805</v>
       </c>
       <c r="R21" t="n">
-        <v>6664350</v>
+        <v>6663985</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2904,32 +2904,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236749</v>
+        <v>130236770</v>
       </c>
       <c r="B22" t="n">
-        <v>97197</v>
+        <v>92214</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631805</v>
+        <v>631788</v>
       </c>
       <c r="R22" t="n">
-        <v>6663985</v>
+        <v>6664350</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3004,7 +3004,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92409</v>
+        <v>92411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3098,32 +3098,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236773</v>
+        <v>130236753</v>
       </c>
       <c r="B24" t="n">
-        <v>92212</v>
+        <v>97199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631687</v>
+        <v>631776</v>
       </c>
       <c r="R24" t="n">
-        <v>6664111</v>
+        <v>6664335</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3195,32 +3195,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130236753</v>
+        <v>130236773</v>
       </c>
       <c r="B25" t="n">
-        <v>97197</v>
+        <v>92214</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631776</v>
+        <v>631687</v>
       </c>
       <c r="R25" t="n">
-        <v>6664335</v>
+        <v>6664111</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3295,7 +3295,7 @@
         <v>130236783</v>
       </c>
       <c r="B26" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>130236767</v>
       </c>
       <c r="B27" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>130236759</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>130236771</v>
       </c>
       <c r="B29" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>130236758</v>
       </c>
       <c r="B30" t="n">
-        <v>96297</v>
+        <v>96299</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>130236768</v>
       </c>
       <c r="B31" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>130236765</v>
       </c>
       <c r="B32" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130236756</v>
       </c>
       <c r="B34" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B35" t="n">
-        <v>8440</v>
+        <v>92059</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R35" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236774</v>
+        <v>130236785</v>
       </c>
       <c r="B36" t="n">
-        <v>92057</v>
+        <v>8440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631623</v>
+        <v>631651</v>
       </c>
       <c r="R36" t="n">
-        <v>6664101</v>
+        <v>6664180</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4362,7 +4362,7 @@
         <v>130236784</v>
       </c>
       <c r="B37" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
         <v>130236750</v>
       </c>
       <c r="B16" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>130236782</v>
       </c>
       <c r="B19" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>130236749</v>
       </c>
       <c r="B21" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>130236770</v>
       </c>
       <c r="B22" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92411</v>
+        <v>92415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>130236753</v>
       </c>
       <c r="B24" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>130236773</v>
       </c>
       <c r="B25" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>130236783</v>
       </c>
       <c r="B26" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,32 +3389,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130236767</v>
+        <v>130236759</v>
       </c>
       <c r="B27" t="n">
-        <v>91534</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631787</v>
+        <v>631838</v>
       </c>
       <c r="R27" t="n">
-        <v>6664306</v>
+        <v>6664323</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236759</v>
+        <v>130236767</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>91534</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631838</v>
+        <v>631787</v>
       </c>
       <c r="R28" t="n">
-        <v>6664323</v>
+        <v>6664306</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3586,7 +3586,7 @@
         <v>130236771</v>
       </c>
       <c r="B29" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>130236758</v>
       </c>
       <c r="B30" t="n">
-        <v>96299</v>
+        <v>96303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236774</v>
+        <v>130236785</v>
       </c>
       <c r="B35" t="n">
-        <v>92059</v>
+        <v>8440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631623</v>
+        <v>631651</v>
       </c>
       <c r="R35" t="n">
-        <v>6664101</v>
+        <v>6664180</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B36" t="n">
-        <v>8440</v>
+        <v>92059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R36" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4362,7 +4362,7 @@
         <v>130236784</v>
       </c>
       <c r="B37" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -3389,32 +3389,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130236759</v>
+        <v>130236767</v>
       </c>
       <c r="B27" t="n">
-        <v>57851</v>
+        <v>91534</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>631838</v>
+        <v>631787</v>
       </c>
       <c r="R27" t="n">
-        <v>6664323</v>
+        <v>6664306</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236767</v>
+        <v>130236759</v>
       </c>
       <c r="B28" t="n">
-        <v>91534</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631787</v>
+        <v>631838</v>
       </c>
       <c r="R28" t="n">
-        <v>6664306</v>
+        <v>6664323</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236785</v>
+        <v>130236774</v>
       </c>
       <c r="B35" t="n">
-        <v>8440</v>
+        <v>92059</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631651</v>
+        <v>631623</v>
       </c>
       <c r="R35" t="n">
-        <v>6664180</v>
+        <v>6664101</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236774</v>
+        <v>130236785</v>
       </c>
       <c r="B36" t="n">
-        <v>92059</v>
+        <v>8440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631623</v>
+        <v>631651</v>
       </c>
       <c r="R36" t="n">
-        <v>6664101</v>
+        <v>6664180</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -2414,32 +2414,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130236803</v>
+        <v>130236816</v>
       </c>
       <c r="B17" t="n">
-        <v>57851</v>
+        <v>5177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631661</v>
+        <v>631624</v>
       </c>
       <c r="R17" t="n">
-        <v>6664002</v>
+        <v>6664012</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2485,11 +2485,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flykt och lockläte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,32 +2511,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130236816</v>
+        <v>130236803</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>57851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631624</v>
+        <v>631661</v>
       </c>
       <c r="R18" t="n">
-        <v>6664012</v>
+        <v>6664002</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2587,6 +2582,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flykt och lockläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2807,32 +2807,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236749</v>
+        <v>130236770</v>
       </c>
       <c r="B21" t="n">
-        <v>97203</v>
+        <v>92220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631805</v>
+        <v>631788</v>
       </c>
       <c r="R21" t="n">
-        <v>6663985</v>
+        <v>6664350</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2904,32 +2904,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236770</v>
+        <v>130236749</v>
       </c>
       <c r="B22" t="n">
-        <v>92220</v>
+        <v>97203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631788</v>
+        <v>631805</v>
       </c>
       <c r="R22" t="n">
-        <v>6664350</v>
+        <v>6663985</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 63008-2025 artfynd.xlsx
+++ b/artfynd/A 63008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1340628</v>
+        <v>124298588</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Husby, 0,5 km SV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631829.9789625958</v>
+        <v>631634</v>
       </c>
       <c r="R2" t="n">
-        <v>6664167.112270116</v>
+        <v>6664079</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,78 +766,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4955707</v>
+        <v>130236749</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Husby, 0,5 km SV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631869.7904052894</v>
+        <v>631805</v>
       </c>
       <c r="R3" t="n">
-        <v>6664172.535009781</v>
+        <v>6663985</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,78 +863,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1340629</v>
+        <v>130236750</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Husby, 0,7 km SV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631642.1807512974</v>
+        <v>631670</v>
       </c>
       <c r="R4" t="n">
-        <v>6664049.046243516</v>
+        <v>6664219</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,92 +960,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123680</v>
+        <v>130236751</v>
       </c>
       <c r="B5" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Husby, 0,8 km SV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631608.3102302161</v>
+        <v>631625</v>
       </c>
       <c r="R5" t="n">
-        <v>6663989.41968561</v>
+        <v>6664213</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,83 +1057,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>död ved</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4955708</v>
+        <v>130236752</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Husby, 0,8 km SV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631608.3102302161</v>
+        <v>631701</v>
       </c>
       <c r="R6" t="n">
-        <v>6663989.41968561</v>
+        <v>6663882</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,78 +1154,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3937008</v>
+        <v>130236753</v>
       </c>
       <c r="B7" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Risbo gård, 0,6 km N-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631902.9695596478</v>
+        <v>631776</v>
       </c>
       <c r="R7" t="n">
-        <v>6664153.756501632</v>
+        <v>6664335</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-06-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-06-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,84 +1251,75 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>blockig granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60900268</v>
+        <v>123680</v>
       </c>
       <c r="B8" t="n">
-        <v>85128</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>426</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsveden 3,5 km SO om Sörsjön, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631813.3590624626</v>
+        <v>631608</v>
       </c>
       <c r="R8" t="n">
-        <v>6664295.816661532</v>
+        <v>6663989</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,27 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2004-09-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2004-09-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ex. i vegetation av piprör, under en 70-årig gran i svag sluttning, i gallrad och ganska trivial barrskog.</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,68 +1363,86 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>70-årig, gallrad gran- och tallskog.</t>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>död ved</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124298004</v>
+        <v>60900268</v>
       </c>
       <c r="B9" t="n">
-        <v>91792</v>
+        <v>87195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Långsveden 3,5 km SO om Sörsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631630</v>
+        <v>631813</v>
       </c>
       <c r="R9" t="n">
-        <v>6664092</v>
+        <v>6664296</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,22 +1466,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2004-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2004-09-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 ex. i vegetation av piprör, under en 70-årig gran i svag sluttning, i gallrad och ganska trivial barrskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,64 +1487,69 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>70-årig, gallrad gran- och tallskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124298588</v>
+        <v>190221</v>
       </c>
       <c r="B10" t="n">
-        <v>96522</v>
+        <v>98215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631634</v>
+        <v>631545</v>
       </c>
       <c r="R10" t="n">
-        <v>6664079</v>
+        <v>6663994</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,22 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,26 +1589,35 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124303074</v>
+        <v>124299477</v>
       </c>
       <c r="B11" t="n">
-        <v>57793</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,45 +1625,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631701</v>
+        <v>631694</v>
       </c>
       <c r="R11" t="n">
-        <v>6663984</v>
+        <v>6664110</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1843,7 +1684,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1694,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,32 +1721,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124299925</v>
+        <v>130236774</v>
       </c>
       <c r="B12" t="n">
-        <v>100451</v>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1915,13 +1756,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631672</v>
+        <v>631623</v>
       </c>
       <c r="R12" t="n">
-        <v>6664080</v>
+        <v>6664101</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,22 +1786,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,22 +1806,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124298903</v>
+        <v>380188</v>
       </c>
       <c r="B13" t="n">
-        <v>91166</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,17 +1849,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Hocksbo, mellan Hocksbo och Risbo, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631694</v>
+        <v>631691</v>
       </c>
       <c r="R13" t="n">
-        <v>6664110</v>
+        <v>6664270</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,22 +1883,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2002-02-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2002-02-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,64 +1899,70 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>PFERF7</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299526</v>
+        <v>124298903</v>
       </c>
       <c r="B14" t="n">
-        <v>91617</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631692</v>
+        <v>631694</v>
       </c>
       <c r="R14" t="n">
-        <v>6664112</v>
+        <v>6664110</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2167,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,12 +2004,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På granlåga tillsammans med ullticka och rosenticka</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,7 +2013,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2210,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124299477</v>
+        <v>130236756</v>
       </c>
       <c r="B15" t="n">
-        <v>91459</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2245,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631694</v>
+        <v>631787</v>
       </c>
       <c r="R15" t="n">
-        <v>6664110</v>
+        <v>6664350</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,22 +2096,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,22 +2116,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236750</v>
+        <v>130236757</v>
       </c>
       <c r="B16" t="n">
-        <v>97203</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631670</v>
+        <v>631626</v>
       </c>
       <c r="R16" t="n">
-        <v>6664219</v>
+        <v>6664192</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2414,48 +2225,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130236816</v>
+        <v>124299526</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631624</v>
+        <v>631692</v>
       </c>
       <c r="R17" t="n">
-        <v>6664012</v>
+        <v>6664112</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2479,12 +2293,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På granlåga tillsammans med ullticka och rosenticka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,28 +2322,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130236803</v>
+        <v>130236770</v>
       </c>
       <c r="B18" t="n">
-        <v>57851</v>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631661</v>
+        <v>631788</v>
       </c>
       <c r="R18" t="n">
-        <v>6664002</v>
+        <v>6664350</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2582,11 +2412,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flykt och lockläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130236782</v>
+        <v>130236771</v>
       </c>
       <c r="B19" t="n">
-        <v>101146</v>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631812</v>
+        <v>631778</v>
       </c>
       <c r="R19" t="n">
-        <v>6664082</v>
+        <v>6664355</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2710,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130236762</v>
+        <v>130236772</v>
       </c>
       <c r="B20" t="n">
-        <v>57851</v>
+        <v>92369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>631777</v>
+        <v>631625</v>
       </c>
       <c r="R20" t="n">
-        <v>6664346</v>
+        <v>6664192</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2807,14 +2632,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236770</v>
+        <v>130236773</v>
       </c>
       <c r="B21" t="n">
-        <v>92220</v>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2842,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631788</v>
+        <v>631687</v>
       </c>
       <c r="R21" t="n">
-        <v>6664350</v>
+        <v>6664111</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2904,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236749</v>
+        <v>124298004</v>
       </c>
       <c r="B22" t="n">
-        <v>97203</v>
+        <v>92564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2939,13 +2764,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631805</v>
+        <v>631630</v>
       </c>
       <c r="R22" t="n">
-        <v>6663985</v>
+        <v>6664092</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,12 +2794,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,12 +2824,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3004,7 +2839,7 @@
         <v>130236781</v>
       </c>
       <c r="B23" t="n">
-        <v>92415</v>
+        <v>92564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3098,32 +2933,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236753</v>
+        <v>130236758</v>
       </c>
       <c r="B24" t="n">
-        <v>97203</v>
+        <v>96458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3133,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>631776</v>
+        <v>631702</v>
       </c>
       <c r="R24" t="n">
-        <v>6664335</v>
+        <v>6663884</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3195,48 +3030,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130236773</v>
+        <v>1160430</v>
       </c>
       <c r="B25" t="n">
-        <v>92220</v>
+        <v>91680</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>631687</v>
+        <v>631575</v>
       </c>
       <c r="R25" t="n">
-        <v>6664111</v>
+        <v>6663982</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3260,12 +3095,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,26 +3111,35 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130236783</v>
+        <v>130236766</v>
       </c>
       <c r="B26" t="n">
-        <v>101146</v>
+        <v>91680</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,21 +3147,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>631850</v>
+        <v>631768</v>
       </c>
       <c r="R26" t="n">
-        <v>6664146</v>
+        <v>6664325</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3392,7 +3236,7 @@
         <v>130236767</v>
       </c>
       <c r="B27" t="n">
-        <v>91534</v>
+        <v>91680</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,32 +3330,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236759</v>
+        <v>130236768</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>91680</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3521,10 +3365,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>631838</v>
+        <v>631680</v>
       </c>
       <c r="R28" t="n">
-        <v>6664323</v>
+        <v>6664120</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3583,48 +3427,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130236771</v>
+        <v>1340628</v>
       </c>
       <c r="B29" t="n">
-        <v>92220</v>
+        <v>92869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,5 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>631778</v>
+        <v>631830</v>
       </c>
       <c r="R29" t="n">
-        <v>6664355</v>
+        <v>6664167</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3648,12 +3492,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3664,26 +3508,35 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130236758</v>
+        <v>1340629</v>
       </c>
       <c r="B30" t="n">
-        <v>96303</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,37 +3544,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,7 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>631702</v>
+        <v>631642</v>
       </c>
       <c r="R30" t="n">
-        <v>6663884</v>
+        <v>6664049</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3745,12 +3598,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3761,26 +3614,35 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130236768</v>
+        <v>1340630</v>
       </c>
       <c r="B31" t="n">
-        <v>91534</v>
+        <v>92869</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,37 +3650,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>631680</v>
+        <v>631578</v>
       </c>
       <c r="R31" t="n">
-        <v>6664120</v>
+        <v>6663976</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3842,12 +3704,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3858,30 +3720,39 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130236765</v>
+        <v>130236759</v>
       </c>
       <c r="B32" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3909,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>631682</v>
+        <v>631838</v>
       </c>
       <c r="R32" t="n">
-        <v>6664177</v>
+        <v>6664323</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3971,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130236780</v>
+        <v>130236762</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3982,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4006,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>631621</v>
+        <v>631777</v>
       </c>
       <c r="R33" t="n">
-        <v>6664176</v>
+        <v>6664346</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4068,32 +3939,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130236756</v>
+        <v>130236763</v>
       </c>
       <c r="B34" t="n">
-        <v>91761</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4103,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>631787</v>
+        <v>631760</v>
       </c>
       <c r="R34" t="n">
-        <v>6664350</v>
+        <v>6664344</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4165,32 +4036,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130236774</v>
+        <v>130236764</v>
       </c>
       <c r="B35" t="n">
-        <v>92059</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>631623</v>
+        <v>631663</v>
       </c>
       <c r="R35" t="n">
-        <v>6664101</v>
+        <v>6664213</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130236785</v>
+        <v>130236765</v>
       </c>
       <c r="B36" t="n">
-        <v>8440</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4273,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>631651</v>
+        <v>631682</v>
       </c>
       <c r="R36" t="n">
-        <v>6664180</v>
+        <v>6664177</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4359,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130236784</v>
+        <v>130236803</v>
       </c>
       <c r="B37" t="n">
-        <v>101146</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4394,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>631842</v>
+        <v>631661</v>
       </c>
       <c r="R37" t="n">
-        <v>6664237</v>
+        <v>6664002</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4432,6 +4303,11 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Flykt och lockläte</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4453,6 +4329,1433 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130236780</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>631621</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6664176</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130236816</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>631624</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6664012</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124303074</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>631701</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6663984</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130236785</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>631651</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6664180</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>65870937</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Risboskogen, 400 m N om Risbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>631791</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6663954</v>
+      </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>71666362</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Risbo 4 km SSO om Sörsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>631796</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6663969</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2004-06-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2004-06-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Några plantor.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3937008</v>
+      </c>
+      <c r="B44" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Risbo gård, 0,6 km N-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>631903</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6664154</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2012-06-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2012-06-03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>blockig granskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130236775</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>631783</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6664373</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4955707</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Husby, 0,5 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>631870</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6664173</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4955708</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>631608</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6663989</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124299925</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>631672</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6664080</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130236782</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>631812</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6664082</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130236783</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>631850</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6664146</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130236784</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>631842</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6664237</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
